--- a/ARM Functions/Move Edits/Scale Shot.xlsx
+++ b/ARM Functions/Move Edits/Scale Shot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\Modded ROM\USUM ARM research\Move Edits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595CAD05-0CFB-4504-A066-5BD0BAAC8B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F61024C-1215-4D0C-B2D7-ADBFD432DB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView minimized="1" xWindow="-32537" yWindow="377" windowWidth="24686" windowHeight="12832" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Edited main" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="89">
   <si>
     <t>Address</t>
   </si>
@@ -107,9 +107,6 @@
     <t>check attacking</t>
   </si>
   <si>
-    <t>cmp r0, 0x0</t>
-  </si>
-  <si>
     <t>mov r2, r4</t>
   </si>
   <si>
@@ -119,18 +116,12 @@
     <t>bl 0x000876F8</t>
   </si>
   <si>
-    <t>000050E3</t>
-  </si>
-  <si>
     <t>0420A0E1</t>
   </si>
   <si>
     <t>0D10A0E3</t>
   </si>
   <si>
-    <t>1200001A</t>
-  </si>
-  <si>
     <t>000C36B0</t>
   </si>
   <si>
@@ -218,69 +209,6 @@
     <t>nop</t>
   </si>
   <si>
-    <t>mov r1, 0x4</t>
-  </si>
-  <si>
-    <t>mov r1, r4</t>
-  </si>
-  <si>
-    <t>bl 0x00092298</t>
-  </si>
-  <si>
-    <t>ldrh r1, [r0, 0xC]</t>
-  </si>
-  <si>
-    <t>Check Mewtwo</t>
-  </si>
-  <si>
-    <t>cmp r1, 0x9C</t>
-  </si>
-  <si>
-    <t>do nothing if not</t>
-  </si>
-  <si>
-    <t>do nothing if in base forme</t>
-  </si>
-  <si>
-    <t>mov r0, 0x18</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>Ice</t>
-  </si>
-  <si>
-    <t>Fairy</t>
-  </si>
-  <si>
-    <t>cmp r0, 0x8</t>
-  </si>
-  <si>
-    <t>cmpne r0, 0xE</t>
-  </si>
-  <si>
-    <t>cmpne r0, 0x11</t>
-  </si>
-  <si>
-    <t>get Target Type</t>
-  </si>
-  <si>
-    <t>mov r1, 0x7</t>
-  </si>
-  <si>
-    <t>mov r0, 0x3D</t>
-  </si>
-  <si>
-    <t>push {r4, r5, lr}</t>
-  </si>
-  <si>
-    <t>b 0x00082D44</t>
-  </si>
-  <si>
-    <t>Mewtwo gets neutral on Fairy, Ice, Steel 0x4E/0x4F</t>
-  </si>
-  <si>
     <t>use Highest Attacking Stat 0x2D</t>
   </si>
   <si>
@@ -293,9 +221,6 @@
     <t>mvn r8, 0x0</t>
   </si>
   <si>
-    <t>ldrb r1, [r0, 0x239]</t>
-  </si>
-  <si>
     <t>F0402DE9</t>
   </si>
   <si>
@@ -374,71 +299,17 @@
     <t>F080BDE8</t>
   </si>
   <si>
-    <t>30402DE9</t>
-  </si>
-  <si>
-    <t>5E2BFEEB</t>
-  </si>
-  <si>
-    <t>0410A0E1</t>
-  </si>
-  <si>
-    <t>2955FEEB</t>
-  </si>
-  <si>
-    <t>BC10D0E1</t>
-  </si>
-  <si>
-    <t>9C0051E3</t>
-  </si>
-  <si>
-    <t>0C00001A</t>
-  </si>
-  <si>
-    <t>3912D0E5</t>
-  </si>
-  <si>
-    <t>0900000A</t>
-  </si>
-  <si>
-    <t>1800A0E3</t>
-  </si>
-  <si>
-    <t>512BFEEB</t>
-  </si>
-  <si>
-    <t>080050E3</t>
-  </si>
-  <si>
-    <t>0E005013</t>
-  </si>
-  <si>
-    <t>0300001A</t>
-  </si>
-  <si>
-    <t>0710A0E3</t>
-  </si>
-  <si>
-    <t>3D00A0E3</t>
-  </si>
-  <si>
-    <t>3040BDE8</t>
-  </si>
-  <si>
-    <t>C417FEEA</t>
-  </si>
-  <si>
-    <t>3080BDE8</t>
-  </si>
-  <si>
     <t>0410A0E3</t>
+  </si>
+  <si>
+    <t>mov r1, 0x2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -511,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -534,7 +405,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -870,16 +740,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
-  <dimension ref="A1:M86"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M58"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" customWidth="1"/>
+    <col min="2" max="2" width="9.2109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -893,23 +763,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="str">
         <f>DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000C36B4</v>
@@ -921,7 +791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13">
       <c r="A5" t="str">
         <f t="shared" ref="A5:A7" si="0">DEC2HEX(HEX2DEC(A4)+4,8)</f>
         <v>000C36B8</v>
@@ -933,7 +803,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>000C36BC</v>
@@ -945,7 +815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>000C36C0</v>
@@ -954,50 +824,50 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13">
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="M10" s="23"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13">
+      <c r="M10" s="22"/>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="str">
         <f t="shared" ref="A13:A57" si="1">DEC2HEX(HEX2DEC(A12)+4,8)</f>
         <v>000FCD14</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="str">
         <f t="shared" si="1"/>
         <v>000FCD18</v>
@@ -1009,7 +879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13">
       <c r="A15" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000FCD1C</v>
@@ -1024,20 +894,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13">
       <c r="A16" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000FCD20</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="7"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7">
       <c r="A17" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000FCD24</v>
@@ -1050,13 +920,13 @@
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7">
       <c r="A18" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000FCD28</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="C18" s="7" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$57)</f>
@@ -1064,71 +934,71 @@
       </c>
       <c r="D18" s="10"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7">
       <c r="A19" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000FCD2C</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000FCD30</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D20" s="15"/>
       <c r="F20" s="15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G20" s="15"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7">
       <c r="A21" s="15" t="str">
         <f t="shared" si="1"/>
         <v>000FCD34</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D21" s="15"/>
       <c r="F21" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="15"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD38</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="G21" s="15"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD38</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>59</v>
       </c>
       <c r="D22" s="15"/>
       <c r="F22" s="15" t="str">
@@ -1137,61 +1007,61 @@
       </c>
       <c r="G22" s="15"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7">
       <c r="A23" s="5" t="str">
         <f t="shared" si="1"/>
         <v>000FCD3C</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD40</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD40</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD48</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD44</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD48</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>26</v>
-      </c>
       <c r="D26" s="5"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7">
       <c r="A27" s="13" t="str">
         <f t="shared" si="1"/>
         <v>000FCD4C</v>
@@ -1204,221 +1074,221 @@
       </c>
       <c r="D27" s="13"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7">
       <c r="A28" s="13" t="str">
         <f t="shared" si="1"/>
         <v>000FCD50</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C28" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD54</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD58</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="13"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD54</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="17" t="s">
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD5C</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D31" s="13"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD60</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD58</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="13" t="s">
+      <c r="D32" s="13"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD64</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD5C</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="17" t="s">
+      <c r="D33" s="13"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD68</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="13"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD60</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="17" t="s">
+      <c r="D34" s="13"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD6C</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="13"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD64</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="17" t="s">
+      <c r="D35" s="13"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD70</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="13"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD68</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="17" t="s">
+      <c r="D36" s="13"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD74</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="13"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD78</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="13"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD6C</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C35" s="17" t="s">
+      <c r="D38" s="13"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD7C</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D35" s="13"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD70</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="13"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD74</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="13"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A38" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD78</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="13"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A39" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD7C</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>47</v>
-      </c>
       <c r="D39" s="13"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4">
       <c r="A40" s="5" t="str">
         <f t="shared" si="1"/>
         <v>000FCD80</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD84</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD84</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="11" t="s">
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD88</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD8C</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A42" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD88</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD8C</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>26</v>
-      </c>
       <c r="D43" s="5"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4">
       <c r="A44" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000FCD90</v>
@@ -1431,148 +1301,148 @@
       </c>
       <c r="D44" s="18"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4">
       <c r="A45" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000FCD94</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D45" s="18"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4">
       <c r="A46" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000FCD98</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C46" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCD9C</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="18" t="s">
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCDA0</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCD9C</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C47" s="19" t="s">
+      <c r="D48" s="18"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCDA4</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D47" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCDA0</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="18"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A49" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCDA4</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="D49" s="18"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5">
       <c r="A50" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000FCDA8</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D50" s="18"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5">
       <c r="A51" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000FCDAC</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="C51" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" s="18"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000FCDB0</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="18"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A52" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000FCDB0</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>46</v>
-      </c>
       <c r="D52" s="18"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5">
       <c r="A53" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000FCDB4</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D53" s="18"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5">
       <c r="A54" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000FCDB8</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D54" s="18"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5">
       <c r="A55" t="str">
         <f t="shared" si="1"/>
         <v>000FCDBC</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C55" t="str">
         <f>SUBSTITUTE(C12,"push","pop")</f>
@@ -1580,29 +1450,29 @@
       </c>
       <c r="D55" s="3"/>
       <c r="E55" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000FCDC0</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="18"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5">
       <c r="A57" t="str">
         <f t="shared" si="1"/>
         <v>000FCDC4</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C57" t="str">
         <f>SUBSTITUTE(C55,"lr","pc")</f>
@@ -1610,383 +1480,8 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5">
       <c r="D58" s="2"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A60" t="str">
-        <f>DEC2HEX(HEX2DEC(A57)+4,8)</f>
-        <v>000FCDC8</v>
-      </c>
-      <c r="B60" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" t="s">
-        <v>78</v>
-      </c>
-      <c r="D60" s="2"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A61" t="str">
-        <f t="shared" ref="A61:A86" si="2">DEC2HEX(HEX2DEC(A60)+4,8)</f>
-        <v>000FCDCC</v>
-      </c>
-      <c r="B61" t="s">
-        <v>87</v>
-      </c>
-      <c r="C61" t="s">
-        <v>34</v>
-      </c>
-      <c r="D61" s="2"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A62" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDD0</v>
-      </c>
-      <c r="B62" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="2"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A63" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDD4</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A64" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDD8</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="7"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A65" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDDC</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D65" s="7"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDE0</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C66" s="7" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$86)</f>
-        <v>bne 0x000FCE30</v>
-      </c>
-      <c r="D66" s="10"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDE4</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D67" s="5"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDE8</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D68" s="5"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDEC</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D69" s="5"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDF0</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDF4</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D71" s="5"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDF8</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C72" s="5" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$86)</f>
-        <v>bne 0x000FCE30</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCDFC</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE00</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D74" s="5"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE04</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C75" s="5" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A$86)</f>
-        <v>beq 0x000FCE30</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A76" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE08</v>
-      </c>
-      <c r="B76" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A77" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE0C</v>
-      </c>
-      <c r="B77" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="15"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A78" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE10</v>
-      </c>
-      <c r="B78" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C78" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A79" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE14</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A80" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE18</v>
-      </c>
-      <c r="B80" s="15">
-        <v>11005013</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A81" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE1C</v>
-      </c>
-      <c r="B81" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C81" s="15" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$86)</f>
-        <v>bne 0x000FCE30</v>
-      </c>
-      <c r="D81" s="15"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A82" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE20</v>
-      </c>
-      <c r="B82" t="s">
-        <v>126</v>
-      </c>
-      <c r="C82" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A83" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE24</v>
-      </c>
-      <c r="B83" t="s">
-        <v>127</v>
-      </c>
-      <c r="C83" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A84" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE28</v>
-      </c>
-      <c r="B84" t="s">
-        <v>128</v>
-      </c>
-      <c r="C84" t="str">
-        <f>SUBSTITUTE(C60,"push", "pop")</f>
-        <v>pop {r4, r5, lr}</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A85" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE2C</v>
-      </c>
-      <c r="B85" t="s">
-        <v>129</v>
-      </c>
-      <c r="C85" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A86" t="str">
-        <f t="shared" si="2"/>
-        <v>000FCE30</v>
-      </c>
-      <c r="B86" t="s">
-        <v>130</v>
-      </c>
-      <c r="C86" t="str">
-        <f>SUBSTITUTE(C84,"lr","pc")</f>
-        <v>pop {r4, r5, pc}</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
